--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484053_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484053_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7926</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.0314</v>
+        <v>-2.2331</v>
       </c>
       <c r="F2" t="n">
-        <v>2.824</v>
+        <v>2.9362</v>
       </c>
       <c r="G2" t="n">
         <v>-2.4929</v>
@@ -610,13 +610,13 @@
         <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6823</v>
+        <v>1.5928</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4885</v>
+        <v>1.2868</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1938</v>
+        <v>0.306</v>
       </c>
       <c r="V2" t="n">
         <v>1.2065</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1037</v>
+        <v>-0.2356</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.9633</v>
+        <v>-2.3487</v>
       </c>
       <c r="F3" t="n">
-        <v>3.067</v>
+        <v>2.1131</v>
       </c>
       <c r="G3" t="n">
         <v>-1.5648</v>
@@ -688,13 +688,13 @@
         <v>2.1822</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6685</v>
+        <v>1.3292</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6917</v>
+        <v>0.3062</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9768</v>
+        <v>1.0229</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5098</v>
+        <v>-0.5291</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.1085</v>
+        <v>-1.3523</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5988</v>
+        <v>0.8232</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3878</v>
@@ -766,13 +766,13 @@
         <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7392</v>
+        <v>0.7199</v>
       </c>
       <c r="T4" t="n">
-        <v>0.822</v>
+        <v>0.5782</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0828</v>
+        <v>0.1416</v>
       </c>
       <c r="V4" t="n">
         <v>-0.266</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANCHEZ</t>
+          <t>S. RODRIGUEZ ALEJANDRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2005</v>
+        <v>-0.9379</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2486</v>
+        <v>1.6797</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0481</v>
+        <v>-2.6177</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9084</v>
+        <v>-1.9129</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2855</v>
+        <v>-0.2572</v>
       </c>
       <c r="I5" t="n">
-        <v>0.377</v>
+        <v>-1.6557</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0834</v>
+        <v>1.2805</v>
       </c>
       <c r="K5" t="n">
-        <v>0.121</v>
+        <v>1.8803</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0376</v>
+        <v>-0.5999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9918</v>
+        <v>-3.1933</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4064</v>
+        <v>-2.1375</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4146</v>
+        <v>-1.0558</v>
       </c>
       <c r="P5" t="n">
+        <v>0.7935</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.1984</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-0.9919</v>
-      </c>
       <c r="R5" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1723</v>
+        <v>-0.1558</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.34</v>
+        <v>-0.0056</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5124</v>
+        <v>-0.1503</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.266</v>
+        <v>0.3373</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X5" t="n">
         <v>-0.266</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ ALEJANDRE</t>
+          <t>J. MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3205</v>
+        <v>-1.0525</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5777</v>
+        <v>-1.0445</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.8982</v>
+        <v>-0.008</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9129</v>
+        <v>-0.9084</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2572</v>
+        <v>-1.2855</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6557</v>
+        <v>0.377</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2805</v>
+        <v>0.0834</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8803</v>
+        <v>0.121</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5999</v>
+        <v>-0.0376</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.1933</v>
+        <v>-0.9918</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.1375</v>
+        <v>-1.4064</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0558</v>
+        <v>0.4146</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.1984</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.7935</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-0.1984</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.9919</v>
-      </c>
       <c r="S6" t="n">
-        <v>-0.5384</v>
+        <v>0.3203</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1076</v>
+        <v>-0.136</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4308</v>
+        <v>0.4562</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3373</v>
+        <v>-0.266</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>-0.266</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1845</v>
+        <v>-1.5052</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2239</v>
+        <v>-0.6287</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9607</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-3.1339</v>
@@ -1000,13 +1000,13 @@
         <v>2.1822</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6297</v>
+        <v>0.0496</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.595</v>
+        <v>0.0001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0347</v>
+        <v>0.0495</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6032</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.3834</v>
+        <v>-4.4681</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.0646</v>
+        <v>-3.4298</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3188</v>
+        <v>-1.0383</v>
       </c>
       <c r="G8" t="n">
         <v>-9.4564</v>
@@ -1078,13 +1078,13 @@
         <v>1.9838</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.34</v>
+        <v>0.5754</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2209</v>
+        <v>0.4139</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1191</v>
+        <v>0.1615</v>
       </c>
       <c r="V8" t="n">
         <v>3.6194</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.651</v>
+        <v>-6.0849</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7807</v>
+        <v>-3.9621</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8702</v>
+        <v>-2.1227</v>
       </c>
       <c r="G9" t="n">
         <v>-5.9074</v>
@@ -1156,13 +1156,13 @@
         <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9823</v>
+        <v>0.5484</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4479</v>
+        <v>0.2665</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5344</v>
+        <v>0.2819</v>
       </c>
       <c r="V9" t="n">
         <v>0.266</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-11.7528</v>
+        <v>-10.6895</v>
       </c>
       <c r="E10" t="n">
-        <v>-8.2828</v>
+        <v>-7.4439</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.4701</v>
+        <v>-3.2456</v>
       </c>
       <c r="G10" t="n">
         <v>-6.3959</v>
@@ -1234,13 +1234,13 @@
         <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5281</v>
+        <v>-0.4648</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.1586</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5306</v>
+        <v>-0.3061</v>
       </c>
       <c r="V10" t="n">
         <v>0.3373</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.1545</v>
+        <v>-11.5259</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.8074</v>
+        <v>-7.2349</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.3471</v>
+        <v>-4.291</v>
       </c>
       <c r="G11" t="n">
         <v>-5.6295</v>
@@ -1312,13 +1312,13 @@
         <v>0.7935</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2039</v>
+        <v>-0.5753</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7991</v>
+        <v>-0.2266</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4048</v>
+        <v>-0.3486</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1469</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-37.2607</v>
+        <v>-36.3256</v>
       </c>
       <c r="E12" t="n">
-        <v>-28.9335</v>
+        <v>-27.9983</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.327199999999999</v>
+        <v>-8.327299999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-37.7899</v>
@@ -1390,10 +1390,10 @@
         <v>14.8786</v>
       </c>
       <c r="S12" t="n">
-        <v>3.004499999999999</v>
+        <v>3.939699999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.39</v>
+        <v>2.3249</v>
       </c>
       <c r="U12" t="n">
         <v>1.6146</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.3111</v>
+        <v>12.2848</v>
       </c>
       <c r="E13" t="n">
-        <v>10.3396</v>
+        <v>9.013199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9715</v>
+        <v>3.2716</v>
       </c>
       <c r="G13" t="n">
         <v>11.1041</v>
@@ -1468,13 +1468,13 @@
         <v>1.3887</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0762</v>
+        <v>1.05</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2957</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2195</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-0.266</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.8857</v>
+        <v>6.7488</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2869</v>
+        <v>1.491</v>
       </c>
       <c r="F14" t="n">
-        <v>5.5988</v>
+        <v>5.2579</v>
       </c>
       <c r="G14" t="n">
         <v>3.6049</v>
@@ -1546,13 +1546,13 @@
         <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4358</v>
+        <v>0.2989</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3683</v>
+        <v>-0.1643</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8041</v>
+        <v>0.4632</v>
       </c>
       <c r="V14" t="n">
         <v>0.266</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0781</v>
+        <v>6.6129</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5886</v>
+        <v>0.4865</v>
       </c>
       <c r="F15" t="n">
-        <v>5.4895</v>
+        <v>6.1263</v>
       </c>
       <c r="G15" t="n">
         <v>7.1569</v>
@@ -1624,13 +1624,13 @@
         <v>2.7774</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6864</v>
+        <v>-0.1517</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2436</v>
+        <v>-0.3457</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4428</v>
+        <v>0.194</v>
       </c>
       <c r="V15" t="n">
         <v>0.7979000000000001</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2107</v>
+        <v>5.6886</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2009</v>
+        <v>3.303</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0098</v>
+        <v>2.3856</v>
       </c>
       <c r="G16" t="n">
         <v>3.8441</v>
@@ -1702,13 +1702,13 @@
         <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3673</v>
+        <v>0.1105</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0679</v>
+        <v>0.0341</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2994</v>
+        <v>0.0764</v>
       </c>
       <c r="V16" t="n">
         <v>0.9405</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2856</v>
+        <v>4.477</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6258</v>
+        <v>-0.4218</v>
       </c>
       <c r="F17" t="n">
-        <v>4.9115</v>
+        <v>4.8988</v>
       </c>
       <c r="G17" t="n">
         <v>5.691</v>
@@ -1780,13 +1780,13 @@
         <v>2.7774</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6038</v>
+        <v>-0.4124</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8615</v>
+        <v>-0.6574</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2577</v>
+        <v>0.245</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6032</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3348</v>
+        <v>3.731</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6413</v>
+        <v>-2.4372</v>
       </c>
       <c r="F18" t="n">
-        <v>5.9761</v>
+        <v>6.1682</v>
       </c>
       <c r="G18" t="n">
         <v>1.4788</v>
@@ -1858,13 +1858,13 @@
         <v>2.9758</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3424</v>
+        <v>0.0538</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1813</v>
+        <v>0.0228</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1611</v>
+        <v>0.031</v>
       </c>
       <c r="V18" t="n">
         <v>1.2065</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.1808</v>
+        <v>3.5489</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1923</v>
+        <v>0.0117</v>
       </c>
       <c r="F19" t="n">
-        <v>3.3731</v>
+        <v>3.5372</v>
       </c>
       <c r="G19" t="n">
         <v>4.1767</v>
@@ -1936,13 +1936,13 @@
         <v>1.9838</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9959</v>
+        <v>-0.6278</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.7935</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0016</v>
+        <v>0.1657</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1143</v>
+        <v>2.4366</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6055</v>
+        <v>1.7075</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5088</v>
+        <v>0.729</v>
       </c>
       <c r="G20" t="n">
         <v>2.3445</v>
@@ -2014,13 +2014,13 @@
         <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6864</v>
+        <v>-0.3642</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3741</v>
+        <v>-0.272</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3124</v>
+        <v>-0.0922</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3373</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. BLÁZQUEZ FARRIOL</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3658</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2733</v>
+        <v>-0.1108</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0926</v>
+        <v>-0.5278</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2206</v>
+        <v>1.0116</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4992</v>
+        <v>1.285</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2786</v>
+        <v>-0.2735</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1008</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1008</v>
+        <v>0.7311</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.8306</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3214</v>
+        <v>1.1111</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2786</v>
+        <v>0.5572</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5952</v>
+        <v>1.3887</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5952</v>
+        <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5339</v>
+        <v>-0.3599</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3741</v>
+        <v>-0.0113</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1599</v>
+        <v>-0.3486</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2065</v>
+        <v>-2.6789</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2065</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>A. BLÁZQUEZ FARRIOL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9394</v>
+        <v>-1.1975</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.723</v>
+        <v>-0.2733</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2164</v>
+        <v>-0.9242</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0116</v>
+        <v>-0.2206</v>
       </c>
       <c r="H22" t="n">
-        <v>1.285</v>
+        <v>-0.4992</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2735</v>
+        <v>0.2786</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.1008</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7311</v>
+        <v>0.1008</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8306</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1111</v>
+        <v>-0.3214</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5538999999999999</v>
+        <v>-0.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5572</v>
+        <v>0.2786</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3887</v>
+        <v>0.5952</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3887</v>
+        <v>0.5952</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6608</v>
+        <v>-0.3656</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.3741</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0373</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.6789</v>
+        <v>-1.2065</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.6789</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.835</v>
+        <v>-3.7109</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2385</v>
+        <v>-4.4426</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4035</v>
+        <v>0.7317</v>
       </c>
       <c r="G23" t="n">
         <v>-2.402</v>
@@ -2248,13 +2248,13 @@
         <v>0.7935</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3605</v>
+        <v>0.4846</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1814</v>
+        <v>-0.0226</v>
       </c>
       <c r="U23" t="n">
-        <v>0.179</v>
+        <v>0.5072</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6032</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>37.2609</v>
+        <v>39.9816</v>
       </c>
       <c r="E24" t="n">
-        <v>8.327299999999999</v>
+        <v>8.327200000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>28.9336</v>
+        <v>31.6543</v>
       </c>
       <c r="G24" t="n">
         <v>37.79</v>
@@ -2326,13 +2326,13 @@
         <v>19.8385</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.0044</v>
+        <v>-0.2838</v>
       </c>
       <c r="T24" t="n">
         <v>-1.6147</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.39</v>
+        <v>1.3309</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4842</v>
@@ -2341,7 +2341,7 @@
         <v>4.0089</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.492999999999999</v>
+        <v>-6.493</v>
       </c>
     </row>
   </sheetData>
